--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70F55FF5-E8FE-489A-AD74-8F1794740A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC05E4-C78A-4ABE-AB06-BDAC14BAECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
   <si>
     <t>사례명</t>
   </si>
@@ -129,21 +129,12 @@
     <t>Slurry TBM</t>
   </si>
   <si>
-    <t>난징 지하철 line 10</t>
-  </si>
-  <si>
     <t>개착식</t>
   </si>
   <si>
-    <t>Gotthard Base Tunnel(고트하르트 베이스 터널)</t>
-  </si>
-  <si>
     <t>암반</t>
   </si>
   <si>
-    <t>보통</t>
-  </si>
-  <si>
     <t>안정성·시공성</t>
   </si>
   <si>
@@ -175,6 +166,29 @@
   </si>
   <si>
     <t>장기안정성</t>
+  </si>
+  <si>
+    <t>Marmaray Project – Üsküdar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매우높음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Folgefonna Tunnel</t>
+  </si>
+  <si>
+    <t>고지압</t>
+  </si>
+  <si>
+    <t>Varberg Tunnel (West Coast Line)</t>
+  </si>
+  <si>
+    <t>Fehmarnbelt Fixed Link</t>
+  </si>
+  <si>
+    <t>Hong Kong–Zhuhai–Macao Bridge Immersed Tunnel</t>
   </si>
 </sst>
 </file>
@@ -583,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -754,12 +768,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
@@ -768,59 +782,59 @@
         <v>13</v>
       </c>
       <c r="E6" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1">
-        <v>4.78</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1">
-        <v>2450</v>
+        <v>500</v>
       </c>
       <c r="F7" s="1">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="J7" s="1">
-        <v>57</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
@@ -829,7 +843,7 @@
         <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1">
         <v>80</v>
@@ -841,10 +855,10 @@
         <v>14</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="J8" s="1">
         <v>1.0569999999999999</v>
@@ -852,7 +866,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>18</v>
@@ -873,10 +887,10 @@
         <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J9" s="1">
         <v>16.2</v>
@@ -884,10 +898,10 @@
     </row>
     <row r="10" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
@@ -908,7 +922,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -916,7 +930,7 @@
     </row>
     <row r="11" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>30</v>
@@ -925,13 +939,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1">
-        <v>55</v>
+        <v>32.5</v>
       </c>
       <c r="F11" s="1">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>14</v>
@@ -943,12 +957,12 @@
         <v>22</v>
       </c>
       <c r="J11" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
@@ -972,14 +986,111 @@
         <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J12" s="1">
         <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>25</v>
+      </c>
+      <c r="F13">
+        <v>9.5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>8.5</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>8.5</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDC05E4-C78A-4ABE-AB06-BDAC14BAECE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F726CE4-D82D-4EA0-BC36-F0208DAF5475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="91">
   <si>
     <t>사례명</t>
   </si>
@@ -189,13 +189,133 @@
   </si>
   <si>
     <t>Hong Kong–Zhuhai–Macao Bridge Immersed Tunnel</t>
+  </si>
+  <si>
+    <t>Crossrail C300 Western Running Tunnels</t>
+  </si>
+  <si>
+    <t>지하수제어</t>
+  </si>
+  <si>
+    <t>Barcelona Metro Line 9 (L9 South)</t>
+  </si>
+  <si>
+    <t>대구경 안정성</t>
+  </si>
+  <si>
+    <t>Delhi Metro Phase III Underground</t>
+  </si>
+  <si>
+    <t>Guangzhou Metro Line 3</t>
+  </si>
+  <si>
+    <t>Shanghai Metro Line 7</t>
+  </si>
+  <si>
+    <t>Thames Tideway Tunnel</t>
+  </si>
+  <si>
+    <t>Shanghai Yangtze River Tunnel</t>
+  </si>
+  <si>
+    <t>수압·수밀관리</t>
+  </si>
+  <si>
+    <t>Nanjing Yangtze River Tunnel</t>
+  </si>
+  <si>
+    <t>지반안정성</t>
+  </si>
+  <si>
+    <t>Busan Subway Line 2 River Crossing</t>
+  </si>
+  <si>
+    <t>Guangzhou Pearl River Tunnel</t>
+  </si>
+  <si>
+    <t>굴진안정성</t>
+  </si>
+  <si>
+    <t>Kishanganga Hydropower Tunnel</t>
+  </si>
+  <si>
+    <t>Niagara Tunnel Project (NATM section)</t>
+  </si>
+  <si>
+    <t>중간</t>
+  </si>
+  <si>
+    <t>고수압</t>
+  </si>
+  <si>
+    <t>내구성·안정성</t>
+  </si>
+  <si>
+    <t>Ghomri Tunnel</t>
+  </si>
+  <si>
+    <t>Qinghai-Tibet Railway Tunnel Section</t>
+  </si>
+  <si>
+    <t>동결지반·고지압</t>
+  </si>
+  <si>
+    <t>지반보강</t>
+  </si>
+  <si>
+    <t>Alborz Tunnel</t>
+  </si>
+  <si>
+    <t>Hong Kong–Zhuhai–Macao Bridge Tunnel</t>
+  </si>
+  <si>
+    <t>접합부 방수관리</t>
+  </si>
+  <si>
+    <t>내구성·장기안정성</t>
+  </si>
+  <si>
+    <t>Tsuen Wan Line Immersed Tube</t>
+  </si>
+  <si>
+    <t>시공정밀도</t>
+  </si>
+  <si>
+    <t>Transbay Tube</t>
+  </si>
+  <si>
+    <t>내진·접합부관리</t>
+  </si>
+  <si>
+    <t>Limfjord Tunnel (immersed section)</t>
+  </si>
+  <si>
+    <t>부력·안정성</t>
+  </si>
+  <si>
+    <t>Second Avenue Subway Phase 1 (Cut &amp; Cover)</t>
+  </si>
+  <si>
+    <t>Singapore Downtown Line Stage 1 (Cut &amp; Cover)</t>
+  </si>
+  <si>
+    <t>Berlin U5 Extension (Cut &amp; Cover)</t>
+  </si>
+  <si>
+    <t>문화재 보호</t>
+  </si>
+  <si>
+    <t>Copenhagen Cityringen (Station Sections)</t>
+  </si>
+  <si>
+    <t>Nanjing Metro Line 10 (Olympic–Zhongsheng)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -232,6 +352,13 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -265,12 +392,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -283,9 +411,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{7B0C8508-4067-4A0C-9BAD-C3AF8E56C633}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -597,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -1088,6 +1218,806 @@
         <v>6.7</v>
       </c>
     </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4">
+        <v>30</v>
+      </c>
+      <c r="F16" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4">
+        <v>20</v>
+      </c>
+      <c r="F18" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="4">
+        <v>18</v>
+      </c>
+      <c r="F19" s="4">
+        <v>6.3</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="4">
+        <v>20</v>
+      </c>
+      <c r="F20" s="4">
+        <v>6.2</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="4">
+        <v>35</v>
+      </c>
+      <c r="F21" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="4">
+        <v>40</v>
+      </c>
+      <c r="F22" s="4">
+        <v>15</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="4">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="4">
+        <v>50</v>
+      </c>
+      <c r="F23" s="4">
+        <v>14.9</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="4">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="4">
+        <v>30</v>
+      </c>
+      <c r="F24" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="4">
+        <v>35</v>
+      </c>
+      <c r="F25" s="4">
+        <v>11.6</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J25" s="4">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="4">
+        <v>7</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="4">
+        <v>140</v>
+      </c>
+      <c r="F27" s="4">
+        <v>14.4</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" s="4">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4">
+        <v>300</v>
+      </c>
+      <c r="F28" s="4">
+        <v>10</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4">
+        <v>600</v>
+      </c>
+      <c r="F29" s="4">
+        <v>9</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4">
+        <v>800</v>
+      </c>
+      <c r="F30" s="4">
+        <v>9.5</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" s="4">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="4">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="4">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="4">
+        <v>40</v>
+      </c>
+      <c r="F32" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="4">
+        <v>30</v>
+      </c>
+      <c r="F33" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="4">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="4">
+        <v>41</v>
+      </c>
+      <c r="F34" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="4">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="4">
+        <v>10</v>
+      </c>
+      <c r="F35" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J35" s="4">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="4">
+        <v>20</v>
+      </c>
+      <c r="F36" s="4">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="4">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="4">
+        <v>18</v>
+      </c>
+      <c r="F37" s="4">
+        <v>9</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="4">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="4">
+        <v>15</v>
+      </c>
+      <c r="F38" s="4">
+        <v>9</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J38" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="4">
+        <v>20</v>
+      </c>
+      <c r="F39" s="4">
+        <v>10</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="4">
+        <v>8</v>
+      </c>
+      <c r="F40" s="4">
+        <v>5</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="4">
+        <v>3.94</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F726CE4-D82D-4EA0-BC36-F0208DAF5475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680BCA64-BC79-4348-96E1-F2BC189BBA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="11520" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="105">
   <si>
     <t>사례명</t>
   </si>
@@ -293,29 +293,78 @@
     <t>부력·안정성</t>
   </si>
   <si>
-    <t>Second Avenue Subway Phase 1 (Cut &amp; Cover)</t>
-  </si>
-  <si>
-    <t>Singapore Downtown Line Stage 1 (Cut &amp; Cover)</t>
-  </si>
-  <si>
-    <t>Berlin U5 Extension (Cut &amp; Cover)</t>
-  </si>
-  <si>
-    <t>문화재 보호</t>
-  </si>
-  <si>
-    <t>Copenhagen Cityringen (Station Sections)</t>
-  </si>
-  <si>
     <t>Nanjing Metro Line 10 (Olympic–Zhongsheng)</t>
+  </si>
+  <si>
+    <t>Slurry TBM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shiraz Metro Line 3(SM3)</t>
+  </si>
+  <si>
+    <t>Nanchang Metro Line 4</t>
+  </si>
+  <si>
+    <t>하천 하부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grand Paris Express-line14</t>
+  </si>
+  <si>
+    <t>Grand Paris Express-line15</t>
+  </si>
+  <si>
+    <t>하천 하부</t>
+  </si>
+  <si>
+    <t>FHWA Cut &amp; Cover Box Tunnel</t>
+  </si>
+  <si>
+    <t>도시복합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>높음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지하수제어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delhi Metro Cut &amp; Cover Tunnel (India)</t>
+  </si>
+  <si>
+    <t>Dublin Port Tunnel (Cut &amp; Cover Section)</t>
+  </si>
+  <si>
+    <t>연약지반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>North-South Line Extension Singapore (Cut &amp; Cover Tunnel Section)</t>
+  </si>
+  <si>
+    <t>도심지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marmaray Tunnel (Kazliçeşme(유럽) ~ Ayrılıkçeşme(아시아) 지하 구간)</t>
+  </si>
+  <si>
+    <t>도심지 및 해저 연결부</t>
+  </si>
+  <si>
+    <t>청계천 복원 지하도로</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,23 +390,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -396,22 +438,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -727,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -739,34 +778,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -775,30 +814,30 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="3">
         <v>80</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="3">
         <v>8.5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="3">
         <v>5</v>
       </c>
     </row>
@@ -809,29 +848,29 @@
       <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="1">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="3">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="1">
-        <v>1</v>
+      <c r="J3" s="3">
+        <v>1.02</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -841,29 +880,29 @@
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1">
-        <v>80</v>
-      </c>
-      <c r="F4" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="3">
+        <v>58</v>
+      </c>
+      <c r="F4" s="3">
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1">
-        <v>5</v>
+      <c r="J4" s="3">
+        <v>1.4</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -873,29 +912,29 @@
       <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1">
-        <v>55</v>
-      </c>
-      <c r="F5" s="1">
-        <v>7</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="3">
+        <v>32</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="1">
-        <v>5</v>
+      <c r="J5" s="3">
+        <v>1.7</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -905,28 +944,28 @@
       <c r="B6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>18</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="3">
         <v>10</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="3">
         <v>1.8</v>
       </c>
     </row>
@@ -937,28 +976,28 @@
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="3">
         <v>500</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <v>10</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="3">
         <v>11.1</v>
       </c>
     </row>
@@ -969,28 +1008,28 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="1">
-        <v>80</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="E8" s="3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="3">
         <v>1.0569999999999999</v>
       </c>
     </row>
@@ -1001,29 +1040,29 @@
       <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1">
-        <v>80</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="1">
-        <v>16.2</v>
+      <c r="J9" s="3">
+        <v>12.1</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1033,29 +1072,29 @@
       <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="1">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3">
+        <v>22.74</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="1">
-        <v>10</v>
+      <c r="J10" s="3">
+        <v>10.79</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="34.799999999999997" x14ac:dyDescent="0.4">
@@ -1065,28 +1104,28 @@
       <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="3">
         <v>32.5</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="3">
         <v>7.5</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="1" t="s">
+      <c r="H11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="3">
         <v>4</v>
       </c>
     </row>
@@ -1097,29 +1136,29 @@
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="1">
-        <v>80</v>
-      </c>
-      <c r="F12" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="E12" s="3">
+        <v>30</v>
+      </c>
+      <c r="F12" s="3">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="J12" s="1">
-        <v>5</v>
+      <c r="J12" s="3">
+        <v>3.7</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
@@ -1219,803 +1258,995 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="2">
         <v>30</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>6.2</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="2">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="2">
         <v>25</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>11.5</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="4" t="s">
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="2">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="2">
         <v>20</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>6.5</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="2">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="2">
         <v>18</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>6.3</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="4" t="s">
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="2">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="2">
         <v>20</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>6.2</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="4" t="s">
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="2">
         <v>35</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>7.2</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="4" t="s">
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="2">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="2">
+        <v>40</v>
+      </c>
+      <c r="F22" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="2">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="2">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="2">
+        <v>30</v>
+      </c>
+      <c r="F24" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2">
+        <v>35</v>
+      </c>
+      <c r="F25" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J26" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="2">
+        <v>140</v>
+      </c>
+      <c r="F27" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="2">
+        <v>300</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J28" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="2">
+        <v>600</v>
+      </c>
+      <c r="F29" s="2">
+        <v>9</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J29" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="2">
+        <v>800</v>
+      </c>
+      <c r="F30" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E31" s="2">
+        <v>30</v>
+      </c>
+      <c r="F31" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2">
         <v>40</v>
       </c>
-      <c r="F22" s="4">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F32" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="2">
+        <v>30</v>
+      </c>
+      <c r="F33" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="2">
+        <v>41</v>
+      </c>
+      <c r="F34" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="2">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="2">
+        <v>10</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="2">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="2">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="2">
+        <v>15</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="2">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J39" s="2">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2">
+        <v>8</v>
+      </c>
+      <c r="F40" s="2">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="4">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="H40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J40" s="2">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41">
+        <v>27</v>
+      </c>
+      <c r="F41">
+        <v>9.36</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s">
+        <v>70</v>
+      </c>
+      <c r="J41">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42">
+        <v>6.28</v>
+      </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" t="s">
+        <v>36</v>
+      </c>
+      <c r="J42">
+        <v>2.0070000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J43">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44">
+        <v>25</v>
+      </c>
+      <c r="F44">
+        <v>10</v>
+      </c>
+      <c r="G44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="4">
-        <v>50</v>
-      </c>
-      <c r="F23" s="4">
-        <v>14.9</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" s="4">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E45">
         <v>30</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="4">
-        <v>30</v>
-      </c>
-      <c r="F24" s="4">
-        <v>7.5</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="4">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="4">
-        <v>11.6</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J25" s="4">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F26" s="4">
-        <v>7</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="4">
-        <v>140</v>
-      </c>
-      <c r="F27" s="4">
-        <v>14.4</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J27" s="4">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="4">
-        <v>300</v>
-      </c>
-      <c r="F28" s="4">
-        <v>10</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J28" s="4">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="4">
-        <v>600</v>
-      </c>
-      <c r="F29" s="4">
-        <v>9</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="4">
-        <v>800</v>
-      </c>
-      <c r="F30" s="4">
-        <v>9.5</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J30" s="4">
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="4">
-        <v>30</v>
-      </c>
-      <c r="F31" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="J31" s="4">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="4">
-        <v>40</v>
-      </c>
-      <c r="F32" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" s="4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="4">
-        <v>30</v>
-      </c>
-      <c r="F33" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="J33" s="4">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="4">
-        <v>41</v>
-      </c>
-      <c r="F34" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J34" s="4">
+      <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46">
+        <v>11</v>
+      </c>
+      <c r="G46" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46">
         <v>5.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="4">
-        <v>10</v>
-      </c>
-      <c r="F35" s="4">
-        <v>8.5</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J35" s="4">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="4">
-        <v>20</v>
-      </c>
-      <c r="F36" s="4">
-        <v>10</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J36" s="4">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A37" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="4">
-        <v>18</v>
-      </c>
-      <c r="F37" s="4">
-        <v>9</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J37" s="4">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A38" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="4">
-        <v>15</v>
-      </c>
-      <c r="F38" s="4">
-        <v>9</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="J38" s="4">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A39" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="4">
-        <v>20</v>
-      </c>
-      <c r="F39" s="4">
-        <v>10</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J39" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A40" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="4">
-        <v>8</v>
-      </c>
-      <c r="F40" s="4">
-        <v>5</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="4">
-        <v>3.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680BCA64-BC79-4348-96E1-F2BC189BBA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFED00C7-D8FD-4DE9-B489-5707EAAB282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11520" yWindow="1284" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="110">
   <si>
     <t>사례명</t>
   </si>
@@ -245,9 +245,6 @@
     <t>중간</t>
   </si>
   <si>
-    <t>고수압</t>
-  </si>
-  <si>
     <t>내구성·안정성</t>
   </si>
   <si>
@@ -358,13 +355,33 @@
   </si>
   <si>
     <t>청계천 복원 지하도로</t>
+  </si>
+  <si>
+    <t>굴진안정성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grand Paris Express Line 16</t>
+  </si>
+  <si>
+    <t>일본 도쿄만 아쿠아라인 (Tokyo Bay Aqua-Line)</t>
+  </si>
+  <si>
+    <t>Xinsen Avenue Tunnel, Chongqing (지중굴착 190 m 구간(K1+065~K1+255), 지중굴착 155 m 구간(K1+700~K1+855)을 제외한 나머지 구간)</t>
+  </si>
+  <si>
+    <t>영국 런던 실버타운 터널 (Silvertown Tunnel)</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,6 +417,18 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -440,7 +469,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -450,6 +479,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -766,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -814,7 +847,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>12</v>
@@ -895,11 +928,11 @@
       <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
+      <c r="H4" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="J4" s="3">
         <v>1.4</v>
@@ -1027,7 +1060,7 @@
         <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="J8" s="3">
         <v>1.0569999999999999</v>
@@ -1460,7 +1493,7 @@
         <v>19</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2">
         <v>40</v>
@@ -1492,7 +1525,7 @@
         <v>19</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" s="2">
         <v>50</v>
@@ -1524,7 +1557,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" s="2">
         <v>30</v>
@@ -1556,7 +1589,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2">
         <v>35</v>
@@ -1632,10 +1665,10 @@
         <v>68</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J27" s="2">
         <v>10.4</v>
@@ -1643,7 +1676,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>18</v>
@@ -1675,7 +1708,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>18</v>
@@ -1696,10 +1729,10 @@
         <v>26</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="J29" s="2">
         <v>6</v>
@@ -1707,7 +1740,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>18</v>
@@ -1731,7 +1764,7 @@
         <v>47</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J30" s="2">
         <v>10.5</v>
@@ -1739,7 +1772,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>24</v>
@@ -1754,16 +1787,16 @@
         <v>30</v>
       </c>
       <c r="F31" s="2">
-        <v>8.5</v>
+        <v>23.6</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>27</v>
+      <c r="H31" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2">
         <v>6.7</v>
@@ -1786,16 +1819,16 @@
         <v>40</v>
       </c>
       <c r="F32" s="2">
-        <v>8.5</v>
+        <v>21.8</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>27</v>
+      <c r="H32" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J32" s="2">
         <v>18</v>
@@ -1803,7 +1836,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>24</v>
@@ -1818,16 +1851,16 @@
         <v>30</v>
       </c>
       <c r="F33" s="2">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>27</v>
+      <c r="H33" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J33" s="2">
         <v>1.4</v>
@@ -1835,7 +1868,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>24</v>
@@ -1850,16 +1883,16 @@
         <v>41</v>
       </c>
       <c r="F34" s="2">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>27</v>
+      <c r="H34" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J34" s="2">
         <v>5.8</v>
@@ -1867,7 +1900,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>24</v>
@@ -1882,24 +1915,24 @@
         <v>10</v>
       </c>
       <c r="F35" s="2">
-        <v>8.5</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>27</v>
+      <c r="H35" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J35" s="2">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>31</v>
@@ -1908,7 +1941,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E36" s="2">
         <v>10</v>
@@ -1917,7 +1950,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -1931,13 +1964,13 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>13</v>
@@ -1949,7 +1982,7 @@
         <v>9.1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -1963,16 +1996,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E38" s="2">
         <v>15</v>
@@ -1987,7 +2020,7 @@
         <v>15</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J38" s="2">
         <v>0.4</v>
@@ -1995,7 +2028,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>31</v>
@@ -2027,7 +2060,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>31</v>
@@ -2059,7 +2092,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
@@ -2083,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J41">
         <v>11.75</v>
@@ -2091,7 +2124,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -2123,7 +2156,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
@@ -2155,7 +2188,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
@@ -2164,7 +2197,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>25</v>
@@ -2187,7 +2220,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
         <v>30</v>
@@ -2196,7 +2229,7 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45">
         <v>30</v>
@@ -2210,8 +2243,8 @@
       <c r="H45" t="s">
         <v>15</v>
       </c>
-      <c r="I45" t="s">
-        <v>28</v>
+      <c r="I45" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="J45">
         <v>12.2</v>
@@ -2219,7 +2252,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
         <v>31</v>
@@ -2242,11 +2275,136 @@
       <c r="H46" t="s">
         <v>15</v>
       </c>
-      <c r="I46" t="s">
-        <v>28</v>
+      <c r="I46" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="J46">
         <v>5.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="F47">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="G47" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48">
+        <v>15</v>
+      </c>
+      <c r="F48">
+        <v>14.14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J48">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49">
+        <v>8.5</v>
+      </c>
+      <c r="F49">
+        <v>10.25</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49">
+        <v>0.45500000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="F50">
+        <v>11.91</v>
+      </c>
+      <c r="G50" t="s">
+        <v>45</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFED00C7-D8FD-4DE9-B489-5707EAAB282A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEEC348-1F44-4F64-A1F5-6331718A7D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="0" yWindow="480" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="118">
   <si>
     <t>사례명</t>
   </si>
@@ -375,6 +375,33 @@
   <si>
     <t>-</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수도권 고속철도(SRT) 율현터널(수서~평택)</t>
+  </si>
+  <si>
+    <t>스페인 바르셀로나 지하철 9호선 (L9)</t>
+  </si>
+  <si>
+    <t>이탈리아 로마 지하철 C노선 (Rome Metro Line C)</t>
+  </si>
+  <si>
+    <t>낮음</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울 지하철 9호선 3단계 923공구</t>
+  </si>
+  <si>
+    <t>수압·수밀관리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>침하·변형관리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본 도쿄 도심(오에도선 연장 구간)</t>
   </si>
 </sst>
 </file>
@@ -469,7 +496,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -484,6 +511,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -799,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -882,7 +916,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>20</v>
@@ -894,7 +928,7 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>15</v>
@@ -2405,6 +2439,169 @@
       </c>
       <c r="I50" s="5" t="s">
         <v>16</v>
+      </c>
+      <c r="J50">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
+      <c r="F51">
+        <v>8.02</v>
+      </c>
+      <c r="G51" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>100</v>
+      </c>
+      <c r="E52">
+        <v>30</v>
+      </c>
+      <c r="F52">
+        <v>12.06</v>
+      </c>
+      <c r="G52" t="s">
+        <v>45</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
+        <v>100</v>
+      </c>
+      <c r="E53">
+        <v>30</v>
+      </c>
+      <c r="F53">
+        <v>6.7</v>
+      </c>
+      <c r="G53" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J53">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>117</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" t="s">
+        <v>100</v>
+      </c>
+      <c r="E55">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>7</v>
+      </c>
+      <c r="G55" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="J55" s="6">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/조사 자료 정규화.xlsx
+++ b/data/raw/조사 자료 정규화.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\김진중\수업\5-1\작업용 폴더\tunnel-method-recommender\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEEC348-1F44-4F64-A1F5-6331718A7D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F8DD4F-19C7-4597-8786-34F2CECD31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="11520" windowHeight="10956" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62748EBE-0567-438F-9666-097F55E0F40C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="120">
   <si>
     <t>사례명</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>일본 도쿄 도심(오에도선 연장 구간)</t>
+  </si>
+  <si>
+    <t>Delhi Tunnel (India)</t>
+  </si>
+  <si>
+    <t>공기단축</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -511,13 +517,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -833,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD01B337-0B57-4C9A-A684-A150612B82F4}">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.09765625" customWidth="1"/>
@@ -2568,7 +2570,7 @@
       <c r="I54" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J54" s="6">
+      <c r="J54">
         <v>1.5</v>
       </c>
     </row>
@@ -2594,14 +2596,78 @@
       <c r="G55" t="s">
         <v>45</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="I55" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J55" s="6">
+      <c r="J55">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56">
+        <v>7.5</v>
+      </c>
+      <c r="F56">
+        <v>6.5</v>
+      </c>
+      <c r="G56" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>16</v>
+      </c>
+      <c r="J56">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57">
+        <v>30</v>
+      </c>
+      <c r="F57">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>119</v>
+      </c>
+      <c r="J57">
+        <v>27.5</v>
       </c>
     </row>
   </sheetData>
